--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/144.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/144.xlsx
@@ -426,13 +426,13 @@
         <v>-7.636109746538834</v>
       </c>
       <c r="E2">
-        <v>-20.38449962805961</v>
+        <v>-18.57906128625472</v>
       </c>
       <c r="F2">
-        <v>-3.163227934232381</v>
+        <v>-3.622222998653976</v>
       </c>
       <c r="G2">
-        <v>-12.24581966544357</v>
+        <v>-11.65256189679276</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.683377874533443</v>
       </c>
       <c r="E3">
-        <v>-21.76557944953882</v>
+        <v>-19.46445948932696</v>
       </c>
       <c r="F3">
-        <v>-3.437523575586576</v>
+        <v>-3.309413243274021</v>
       </c>
       <c r="G3">
-        <v>-12.29142284658884</v>
+        <v>-11.51834482273592</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.738336932381312</v>
       </c>
       <c r="E4">
-        <v>-22.25739442820236</v>
+        <v>-19.65260411555302</v>
       </c>
       <c r="F4">
-        <v>-2.733499918519096</v>
+        <v>-3.463670164288539</v>
       </c>
       <c r="G4">
-        <v>-12.05810974008711</v>
+        <v>-11.12804633859825</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.795555769669908</v>
       </c>
       <c r="E5">
-        <v>-21.95635305853349</v>
+        <v>-20.41770039939029</v>
       </c>
       <c r="F5">
-        <v>-2.951903126104199</v>
+        <v>-3.342327593656857</v>
       </c>
       <c r="G5">
-        <v>-11.56107096334178</v>
+        <v>-11.20148527857398</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.854938130953625</v>
       </c>
       <c r="E6">
-        <v>-24.7247009863659</v>
+        <v>-21.14773942643467</v>
       </c>
       <c r="F6">
-        <v>-3.209242915090491</v>
+        <v>-3.437130929437649</v>
       </c>
       <c r="G6">
-        <v>-11.78180811314812</v>
+        <v>-11.33032160802853</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.916063958158869</v>
       </c>
       <c r="E7">
-        <v>-23.74977200676433</v>
+        <v>-21.17887189852559</v>
       </c>
       <c r="F7">
-        <v>-3.338675321777913</v>
+        <v>-3.46914153098403</v>
       </c>
       <c r="G7">
-        <v>-12.00160278415706</v>
+        <v>-11.26084316759753</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.97206228262137</v>
       </c>
       <c r="E8">
-        <v>-24.6521693037891</v>
+        <v>-22.08682203909165</v>
       </c>
       <c r="F8">
-        <v>-2.897756062452807</v>
+        <v>-3.249340039223001</v>
       </c>
       <c r="G8">
-        <v>-12.73367123197277</v>
+        <v>-10.94345364228359</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.016782634086276</v>
       </c>
       <c r="E9">
-        <v>-23.89267570202903</v>
+        <v>-22.39959623075317</v>
       </c>
       <c r="F9">
-        <v>-2.594831215290458</v>
+        <v>-3.069937197329101</v>
       </c>
       <c r="G9">
-        <v>-11.28589717806615</v>
+        <v>-10.37209610463533</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.039873435363852</v>
       </c>
       <c r="E10">
-        <v>-25.50947103224888</v>
+        <v>-23.0642886308127</v>
       </c>
       <c r="F10">
-        <v>-3.12310678744519</v>
+        <v>-3.070293395312305</v>
       </c>
       <c r="G10">
-        <v>-11.38399460070493</v>
+        <v>-10.59845549291863</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.035865592933975</v>
       </c>
       <c r="E11">
-        <v>-25.40976488797372</v>
+        <v>-24.12784714008612</v>
       </c>
       <c r="F11">
-        <v>-2.869261052163906</v>
+        <v>-3.066273328306519</v>
       </c>
       <c r="G11">
-        <v>-10.9460069504937</v>
+        <v>-10.34088073693169</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.002158205600193</v>
       </c>
       <c r="E12">
-        <v>-27.04893356760043</v>
+        <v>-24.49621206533046</v>
       </c>
       <c r="F12">
-        <v>-2.449313570375475</v>
+        <v>-2.706543186497194</v>
       </c>
       <c r="G12">
-        <v>-10.895742284881</v>
+        <v>-9.894790640881935</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.943438428347687</v>
       </c>
       <c r="E13">
-        <v>-26.31265226393482</v>
+        <v>-25.14771386622234</v>
       </c>
       <c r="F13">
-        <v>-2.255104489523936</v>
+        <v>-2.864782897984373</v>
       </c>
       <c r="G13">
-        <v>-11.3986930927529</v>
+        <v>-9.794860475540187</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.870139606360484</v>
       </c>
       <c r="E14">
-        <v>-27.43205900589321</v>
+        <v>-25.09477288146475</v>
       </c>
       <c r="F14">
-        <v>-1.643947445249503</v>
+        <v>-2.595510476560754</v>
       </c>
       <c r="G14">
-        <v>-10.07269069343728</v>
+        <v>-9.238046090636727</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.795093925077434</v>
       </c>
       <c r="E15">
-        <v>-28.5071883619176</v>
+        <v>-26.28859686394142</v>
       </c>
       <c r="F15">
-        <v>-1.944604222462986</v>
+        <v>-2.427121607654476</v>
       </c>
       <c r="G15">
-        <v>-10.31619092533353</v>
+        <v>-9.079828441553785</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.732678281528468</v>
       </c>
       <c r="E16">
-        <v>-28.19482741478291</v>
+        <v>-26.65826174433043</v>
       </c>
       <c r="F16">
-        <v>-1.607006400921659</v>
+        <v>-2.249555256292582</v>
       </c>
       <c r="G16">
-        <v>-10.58830883406527</v>
+        <v>-8.672494848959108</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.692321670324305</v>
       </c>
       <c r="E17">
-        <v>-28.64444368978053</v>
+        <v>-27.17083031998414</v>
       </c>
       <c r="F17">
-        <v>-1.736186983918631</v>
+        <v>-2.225988203682936</v>
       </c>
       <c r="G17">
-        <v>-9.249960223578274</v>
+        <v>-8.255797820888404</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.684089714902549</v>
       </c>
       <c r="E18">
-        <v>-30.16227422394671</v>
+        <v>-27.8150515414236</v>
       </c>
       <c r="F18">
-        <v>-1.854397497400329</v>
+        <v>-1.889474715071874</v>
       </c>
       <c r="G18">
-        <v>-8.835405311444577</v>
+        <v>-8.039801783259533</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.708362408087713</v>
       </c>
       <c r="E19">
-        <v>-31.50397121903823</v>
+        <v>-29.09014971631584</v>
       </c>
       <c r="F19">
-        <v>-0.7702973383759624</v>
+        <v>-1.801854153040756</v>
       </c>
       <c r="G19">
-        <v>-8.158076345470738</v>
+        <v>-7.403738246292829</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.766188172486774</v>
       </c>
       <c r="E20">
-        <v>-32.29221334958877</v>
+        <v>-29.20016828431054</v>
       </c>
       <c r="F20">
-        <v>-1.284912303691127</v>
+        <v>-1.473547300289228</v>
       </c>
       <c r="G20">
-        <v>-8.390969122093294</v>
+        <v>-7.210067991034864</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.847169367533011</v>
       </c>
       <c r="E21">
-        <v>-31.60638733370284</v>
+        <v>-30.59129057077319</v>
       </c>
       <c r="F21">
-        <v>-0.96406821287142</v>
+        <v>-1.406240792076962</v>
       </c>
       <c r="G21">
-        <v>-8.893897738636175</v>
+        <v>-7.379272958729507</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.944650607625856</v>
       </c>
       <c r="E22">
-        <v>-33.51587815543432</v>
+        <v>-30.45654793576178</v>
       </c>
       <c r="F22">
-        <v>-0.3810532943722943</v>
+        <v>-1.195527319092047</v>
       </c>
       <c r="G22">
-        <v>-7.183751685556441</v>
+        <v>-6.999010176800083</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.042958174864658</v>
       </c>
       <c r="E23">
-        <v>-32.08198402214293</v>
+        <v>-30.6311634760972</v>
       </c>
       <c r="F23">
-        <v>-0.2818480142130255</v>
+        <v>-0.8582649863488532</v>
       </c>
       <c r="G23">
-        <v>-8.428776619889501</v>
+        <v>-7.131528961500402</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.133696749913884</v>
       </c>
       <c r="E24">
-        <v>-33.23497778408521</v>
+        <v>-30.90586725614968</v>
       </c>
       <c r="F24">
-        <v>-0.08825606707657269</v>
+        <v>-0.9288410606999682</v>
       </c>
       <c r="G24">
-        <v>-7.606752356442389</v>
+        <v>-6.947711656329298</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.202580689003675</v>
       </c>
       <c r="E25">
-        <v>-35.21044652092291</v>
+        <v>-31.22248732149798</v>
       </c>
       <c r="F25">
-        <v>-0.4121220421816926</v>
+        <v>-0.7330299172914154</v>
       </c>
       <c r="G25">
-        <v>-8.004124653049674</v>
+        <v>-7.224171233316057</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.244818911987213</v>
       </c>
       <c r="E26">
-        <v>-34.45307313354417</v>
+        <v>-31.29848693553102</v>
       </c>
       <c r="F26">
-        <v>-0.9993268430041782</v>
+        <v>-0.780082842505233</v>
       </c>
       <c r="G26">
-        <v>-8.131098216238469</v>
+        <v>-7.193865710102414</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.253042234556988</v>
       </c>
       <c r="E27">
-        <v>-33.13720495968176</v>
+        <v>-31.34306958249739</v>
       </c>
       <c r="F27">
-        <v>-0.3564623796527882</v>
+        <v>-0.6657863650017628</v>
       </c>
       <c r="G27">
-        <v>-8.911005947941741</v>
+        <v>-7.197029932546843</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.227835702347436</v>
       </c>
       <c r="E28">
-        <v>-32.51911782050379</v>
+        <v>-31.27756721008786</v>
       </c>
       <c r="F28">
-        <v>-0.5696907760726033</v>
+        <v>-0.8281761971769667</v>
       </c>
       <c r="G28">
-        <v>-7.962364487942521</v>
+        <v>-7.255774296591484</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.167477491636463</v>
       </c>
       <c r="E29">
-        <v>-34.12307349791293</v>
+        <v>-31.50431385897253</v>
       </c>
       <c r="F29">
-        <v>-0.8287833904832187</v>
+        <v>-0.7910752779403825</v>
       </c>
       <c r="G29">
-        <v>-7.948684186285087</v>
+        <v>-7.695827045774288</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.073373462589856</v>
       </c>
       <c r="E30">
-        <v>-33.36758566847566</v>
+        <v>-31.39470645889898</v>
       </c>
       <c r="F30">
-        <v>-0.4796323287750467</v>
+        <v>-0.6691337976764756</v>
       </c>
       <c r="G30">
-        <v>-8.334779371631058</v>
+        <v>-7.970823300417728</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.94584544659261</v>
       </c>
       <c r="E31">
-        <v>-34.1413247850799</v>
+        <v>-31.06915283599097</v>
       </c>
       <c r="F31">
-        <v>-1.108962925499498</v>
+        <v>-0.7818124736422783</v>
       </c>
       <c r="G31">
-        <v>-8.898694981822345</v>
+        <v>-7.916673846853447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.784673353033427</v>
       </c>
       <c r="E32">
-        <v>-32.11580777517234</v>
+        <v>-30.98572312689782</v>
       </c>
       <c r="F32">
-        <v>-0.9453926697753051</v>
+        <v>-0.6677578794204256</v>
       </c>
       <c r="G32">
-        <v>-9.019321824910143</v>
+        <v>-8.018122160174928</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.592023057885492</v>
       </c>
       <c r="E33">
-        <v>-32.61129211604137</v>
+        <v>-30.51013059166905</v>
       </c>
       <c r="F33">
-        <v>-0.357785282395059</v>
+        <v>-0.8423379662952271</v>
       </c>
       <c r="G33">
-        <v>-8.958277394880733</v>
+        <v>-7.837390755110519</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.368153029749546</v>
       </c>
       <c r="E34">
-        <v>-31.85637535316126</v>
+        <v>-30.13131411012577</v>
       </c>
       <c r="F34">
-        <v>-0.7273995040545872</v>
+        <v>-0.7333306146586317</v>
       </c>
       <c r="G34">
-        <v>-8.337002420650391</v>
+        <v>-7.872749374480262</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.120949357452534</v>
       </c>
       <c r="E35">
-        <v>-31.03831524190412</v>
+        <v>-29.62346981235406</v>
       </c>
       <c r="F35">
-        <v>-0.9703505512542514</v>
+        <v>-0.943682919455927</v>
       </c>
       <c r="G35">
-        <v>-7.85575473256441</v>
+        <v>-8.112098522476641</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.854247616084506</v>
       </c>
       <c r="E36">
-        <v>-31.86187005174401</v>
+        <v>-28.99537966370023</v>
       </c>
       <c r="F36">
-        <v>-0.8867376307178777</v>
+        <v>-1.073194021046616</v>
       </c>
       <c r="G36">
-        <v>-8.63313917962037</v>
+        <v>-8.093229365944369</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.579782289368479</v>
       </c>
       <c r="E37">
-        <v>-29.72469187876278</v>
+        <v>-29.20352823227233</v>
       </c>
       <c r="F37">
-        <v>-1.254329807547172</v>
+        <v>-0.9016416170290464</v>
       </c>
       <c r="G37">
-        <v>-8.963177762478253</v>
+        <v>-7.960043536001021</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.302722813785824</v>
       </c>
       <c r="E38">
-        <v>-29.98015798395864</v>
+        <v>-28.43170374608884</v>
       </c>
       <c r="F38">
-        <v>-1.0598738732096</v>
+        <v>-1.038627077695195</v>
       </c>
       <c r="G38">
-        <v>-8.808882757143458</v>
+        <v>-8.033457673903127</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.036678157950543</v>
       </c>
       <c r="E39">
-        <v>-29.78182137714145</v>
+        <v>-28.02196037641523</v>
       </c>
       <c r="F39">
-        <v>-1.284740831638748</v>
+        <v>-1.233494710631959</v>
       </c>
       <c r="G39">
-        <v>-8.883577465267503</v>
+        <v>-7.72811281876029</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.788465102659614</v>
       </c>
       <c r="E40">
-        <v>-28.25328594078553</v>
+        <v>-27.75115023197979</v>
       </c>
       <c r="F40">
-        <v>-1.235127422782877</v>
+        <v>-0.9820570393906141</v>
       </c>
       <c r="G40">
-        <v>-8.735878506142157</v>
+        <v>-7.709500820570244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.572063375628947</v>
       </c>
       <c r="E41">
-        <v>-29.99168106877938</v>
+        <v>-27.01577017517167</v>
       </c>
       <c r="F41">
-        <v>-0.9676277076012495</v>
+        <v>-1.139267918563516</v>
       </c>
       <c r="G41">
-        <v>-7.763927013061182</v>
+        <v>-7.866657201976899</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.393666920999715</v>
       </c>
       <c r="E42">
-        <v>-28.26172111298626</v>
+        <v>-26.89626151929973</v>
       </c>
       <c r="F42">
-        <v>-1.03934444386602</v>
+        <v>-1.213379464989779</v>
       </c>
       <c r="G42">
-        <v>-8.469593000826965</v>
+        <v>-7.718167187240444</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.264164589618783</v>
       </c>
       <c r="E43">
-        <v>-29.40044859402775</v>
+        <v>-25.64537656643125</v>
       </c>
       <c r="F43">
-        <v>-0.4201588627236534</v>
+        <v>-1.146665239470515</v>
       </c>
       <c r="G43">
-        <v>-8.650648138220673</v>
+        <v>-8.004684657764468</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.184939973206237</v>
       </c>
       <c r="E44">
-        <v>-28.68224414265346</v>
+        <v>-25.9905416532151</v>
       </c>
       <c r="F44">
-        <v>-1.096676580181176</v>
+        <v>-1.160094731804701</v>
       </c>
       <c r="G44">
-        <v>-8.142840040037001</v>
+        <v>-7.420094561156153</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.160118967675973</v>
       </c>
       <c r="E45">
-        <v>-27.93552789553422</v>
+        <v>-25.86025956716655</v>
       </c>
       <c r="F45">
-        <v>-1.165760764839849</v>
+        <v>-1.04785757566459</v>
       </c>
       <c r="G45">
-        <v>-7.998002456983513</v>
+        <v>-7.471896955333023</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.184530526189613</v>
       </c>
       <c r="E46">
-        <v>-26.94713005160623</v>
+        <v>-25.06556749942856</v>
       </c>
       <c r="F46">
-        <v>-0.6259162135376198</v>
+        <v>-1.212464119009685</v>
       </c>
       <c r="G46">
-        <v>-8.181703584020312</v>
+        <v>-7.5161177472173</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.254907068442762</v>
       </c>
       <c r="E47">
-        <v>-25.75595166474348</v>
+        <v>-24.42223091200129</v>
       </c>
       <c r="F47">
-        <v>-0.7139683549855961</v>
+        <v>-1.109516274924568</v>
       </c>
       <c r="G47">
-        <v>-8.128578847708043</v>
+        <v>-7.537912243063914</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.360661519234288</v>
       </c>
       <c r="E48">
-        <v>-26.34425820211677</v>
+        <v>-24.32769966903687</v>
       </c>
       <c r="F48">
-        <v>-1.116021444138753</v>
+        <v>-1.237976178281105</v>
       </c>
       <c r="G48">
-        <v>-8.511799603259199</v>
+        <v>-7.445627643257241</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.494001758584732</v>
       </c>
       <c r="E49">
-        <v>-25.10282180501227</v>
+        <v>-24.20786290947026</v>
       </c>
       <c r="F49">
-        <v>-0.8125912928606968</v>
+        <v>-1.017095323794228</v>
       </c>
       <c r="G49">
-        <v>-7.735138332454976</v>
+        <v>-7.572922328030743</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.642654490313841</v>
       </c>
       <c r="E50">
-        <v>-25.07992099776716</v>
+        <v>-23.35550765569835</v>
       </c>
       <c r="F50">
-        <v>-1.244232008907046</v>
+        <v>-1.110376948656077</v>
       </c>
       <c r="G50">
-        <v>-8.382435903397239</v>
+        <v>-7.639496315104132</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.797264060008399</v>
       </c>
       <c r="E51">
-        <v>-25.738441725798</v>
+        <v>-22.67835146845301</v>
       </c>
       <c r="F51">
-        <v>-0.7886837812485002</v>
+        <v>-1.353841583645477</v>
       </c>
       <c r="G51">
-        <v>-7.980707579439683</v>
+        <v>-7.591362017077777</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.946198053806238</v>
       </c>
       <c r="E52">
-        <v>-23.77000645233889</v>
+        <v>-22.97943852344645</v>
       </c>
       <c r="F52">
-        <v>-1.529557362229516</v>
+        <v>-1.230181241020761</v>
       </c>
       <c r="G52">
-        <v>-8.056220755993044</v>
+        <v>-7.507256880075062</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.079343782214188</v>
       </c>
       <c r="E53">
-        <v>-23.31050345778251</v>
+        <v>-22.06645053754337</v>
       </c>
       <c r="F53">
-        <v>-1.110845804606062</v>
+        <v>-1.271874629138466</v>
       </c>
       <c r="G53">
-        <v>-8.125955049393975</v>
+        <v>-7.686022394462362</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.186502221670997</v>
       </c>
       <c r="E54">
-        <v>-22.32451862963424</v>
+        <v>-21.77702154673872</v>
       </c>
       <c r="F54">
-        <v>-0.8170711037750366</v>
+        <v>-1.344471091585009</v>
       </c>
       <c r="G54">
-        <v>-8.887754656613286</v>
+        <v>-7.661165495210372</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.258666167582565</v>
       </c>
       <c r="E55">
-        <v>-24.26133135206611</v>
+        <v>-21.56801534002805</v>
       </c>
       <c r="F55">
-        <v>-1.20781697787998</v>
+        <v>-1.361554512532943</v>
       </c>
       <c r="G55">
-        <v>-8.635710763042617</v>
+        <v>-7.954333837580257</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.290068872231543</v>
       </c>
       <c r="E56">
-        <v>-22.50242143673327</v>
+        <v>-20.8593279724046</v>
       </c>
       <c r="F56">
-        <v>-1.096574690990632</v>
+        <v>-1.627176318812424</v>
       </c>
       <c r="G56">
-        <v>-7.876175976756098</v>
+        <v>-8.103728475317531</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.275420670656823</v>
       </c>
       <c r="E57">
-        <v>-21.75861866735841</v>
+        <v>-20.53387402656839</v>
       </c>
       <c r="F57">
-        <v>-1.500378120465904</v>
+        <v>-1.458978802776193</v>
       </c>
       <c r="G57">
-        <v>-8.559783783471564</v>
+        <v>-8.32139408411242</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.2155148321893</v>
       </c>
       <c r="E58">
-        <v>-22.26231183041096</v>
+        <v>-20.37791263489843</v>
       </c>
       <c r="F58">
-        <v>-1.17872140122405</v>
+        <v>-1.415660986181599</v>
       </c>
       <c r="G58">
-        <v>-8.658986856444688</v>
+        <v>-8.47607809039129</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.109541964121702</v>
       </c>
       <c r="E59">
-        <v>-22.11495589260604</v>
+        <v>-20.221689590915</v>
       </c>
       <c r="F59">
-        <v>-0.8397286089764086</v>
+        <v>-1.308008843615983</v>
       </c>
       <c r="G59">
-        <v>-10.0849664145047</v>
+        <v>-8.464982425879059</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.963388369213788</v>
       </c>
       <c r="E60">
-        <v>-22.36774940631438</v>
+        <v>-20.07530965777142</v>
       </c>
       <c r="F60">
-        <v>-0.8315501376085691</v>
+        <v>-1.583605850159976</v>
       </c>
       <c r="G60">
-        <v>-8.857801583919443</v>
+        <v>-8.580403444252179</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.780395748678402</v>
       </c>
       <c r="E61">
-        <v>-22.01505454739862</v>
+        <v>-19.72908134888841</v>
       </c>
       <c r="F61">
-        <v>-0.7264145752126586</v>
+        <v>-1.706948099702017</v>
       </c>
       <c r="G61">
-        <v>-9.426489635223286</v>
+        <v>-8.671987059136136</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.570748067122751</v>
       </c>
       <c r="E62">
-        <v>-22.35951358825725</v>
+        <v>-19.43203536851403</v>
       </c>
       <c r="F62">
-        <v>-1.547747482027591</v>
+        <v>-1.824109071684368</v>
       </c>
       <c r="G62">
-        <v>-9.500455945606411</v>
+        <v>-9.039706518677557</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.340408627320318</v>
       </c>
       <c r="E63">
-        <v>-22.03075368620647</v>
+        <v>-19.25375046597311</v>
       </c>
       <c r="F63">
-        <v>-1.355740201732693</v>
+        <v>-1.71049682565561</v>
       </c>
       <c r="G63">
-        <v>-9.618746172285162</v>
+        <v>-9.054624313271177</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.099879780240414</v>
       </c>
       <c r="E64">
-        <v>-21.78838888613478</v>
+        <v>-19.08480613570174</v>
       </c>
       <c r="F64">
-        <v>-1.214149846674382</v>
+        <v>-1.816725004655813</v>
       </c>
       <c r="G64">
-        <v>-10.37465593970692</v>
+        <v>-9.506322288702643</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.854569348204931</v>
       </c>
       <c r="E65">
-        <v>-21.54597840073851</v>
+        <v>-19.48910049211717</v>
       </c>
       <c r="F65">
-        <v>-1.513557445844444</v>
+        <v>-1.81561167886645</v>
       </c>
       <c r="G65">
-        <v>-9.834389759394233</v>
+        <v>-9.210284738027125</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.611612531777735</v>
       </c>
       <c r="E66">
-        <v>-21.6490694122434</v>
+        <v>-19.14084956931897</v>
       </c>
       <c r="F66">
-        <v>-1.663610402289755</v>
+        <v>-1.914241243680773</v>
       </c>
       <c r="G66">
-        <v>-9.503554899436063</v>
+        <v>-9.178804379747481</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.37388398712716</v>
       </c>
       <c r="E67">
-        <v>-21.22552492133739</v>
+        <v>-18.83655623518276</v>
       </c>
       <c r="F67">
-        <v>-0.8994696376989061</v>
+        <v>-1.976253655821747</v>
       </c>
       <c r="G67">
-        <v>-11.3973133142365</v>
+        <v>-9.408367151644072</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.143058006273798</v>
       </c>
       <c r="E68">
-        <v>-20.22179757440945</v>
+        <v>-18.46600256757023</v>
       </c>
       <c r="F68">
-        <v>-1.491136853720273</v>
+        <v>-1.90016148293539</v>
       </c>
       <c r="G68">
-        <v>-10.19272098138601</v>
+        <v>-9.575358207925451</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.918951730604792</v>
       </c>
       <c r="E69">
-        <v>-20.38922182933594</v>
+        <v>-18.86292912709542</v>
       </c>
       <c r="F69">
-        <v>-1.596566486544177</v>
+        <v>-2.193029949827753</v>
       </c>
       <c r="G69">
-        <v>-11.16117799283178</v>
+        <v>-9.700408957722891</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.698184313584056</v>
       </c>
       <c r="E70">
-        <v>-22.09872929595994</v>
+        <v>-19.08461924119212</v>
       </c>
       <c r="F70">
-        <v>-1.905777813926371</v>
+        <v>-1.906112474357102</v>
       </c>
       <c r="G70">
-        <v>-10.83573823657114</v>
+        <v>-9.363889201417571</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.480332194055519</v>
       </c>
       <c r="E71">
-        <v>-20.06725242780125</v>
+        <v>-19.02007833720429</v>
       </c>
       <c r="F71">
-        <v>-1.416327821940852</v>
+        <v>-2.190368405362558</v>
       </c>
       <c r="G71">
-        <v>-10.80212751070515</v>
+        <v>-9.450954922786607</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.261150913043566</v>
       </c>
       <c r="E72">
-        <v>-21.59804721111788</v>
+        <v>-19.06249093125344</v>
       </c>
       <c r="F72">
-        <v>-1.570923545223115</v>
+        <v>-2.204064632000445</v>
       </c>
       <c r="G72">
-        <v>-10.95632722386237</v>
+        <v>-9.71028018302189</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.042616187491715</v>
       </c>
       <c r="E73">
-        <v>-20.67697292276536</v>
+        <v>-19.45652270248522</v>
       </c>
       <c r="F73">
-        <v>-1.534221899074681</v>
+        <v>-2.381279755583551</v>
       </c>
       <c r="G73">
-        <v>-9.755017902335208</v>
+        <v>-9.448816722966486</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.819837222838585</v>
       </c>
       <c r="E74">
-        <v>-21.31912999817637</v>
+        <v>-19.69404485815216</v>
       </c>
       <c r="F74">
-        <v>-1.843579019119767</v>
+        <v>-2.310892549000275</v>
       </c>
       <c r="G74">
-        <v>-10.16612141011945</v>
+        <v>-9.593247029863759</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.595891023823645</v>
       </c>
       <c r="E75">
-        <v>-20.96284676467596</v>
+        <v>-19.22645971435766</v>
       </c>
       <c r="F75">
-        <v>-1.475783892276787</v>
+        <v>-2.522381373874211</v>
       </c>
       <c r="G75">
-        <v>-10.39176937050167</v>
+        <v>-9.27873715583382</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.367026377969573</v>
       </c>
       <c r="E76">
-        <v>-22.93207945470943</v>
+        <v>-19.94087851360937</v>
       </c>
       <c r="F76">
-        <v>-2.351340072544169</v>
+        <v>-2.44601583974493</v>
       </c>
       <c r="G76">
-        <v>-11.04557291696499</v>
+        <v>-9.034837480015129</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.137710936804446</v>
       </c>
       <c r="E77">
-        <v>-21.87650757081366</v>
+        <v>-20.61681365672522</v>
       </c>
       <c r="F77">
-        <v>-2.494745380582013</v>
+        <v>-2.577791697814872</v>
       </c>
       <c r="G77">
-        <v>-10.76320261422395</v>
+        <v>-8.902890448380264</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.906737121477706</v>
       </c>
       <c r="E78">
-        <v>-23.85226495583845</v>
+        <v>-20.82743546264125</v>
       </c>
       <c r="F78">
-        <v>-1.616125069291676</v>
+        <v>-2.49676825377965</v>
       </c>
       <c r="G78">
-        <v>-9.928270829518372</v>
+        <v>-8.47893685571856</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.679209166212061</v>
       </c>
       <c r="E79">
-        <v>-23.7437623099773</v>
+        <v>-21.0005579235054</v>
       </c>
       <c r="F79">
-        <v>-2.192146910176368</v>
+        <v>-2.781023356417703</v>
       </c>
       <c r="G79">
-        <v>-9.600145922445776</v>
+        <v>-8.993485896436486</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.45568710916543</v>
       </c>
       <c r="E80">
-        <v>-22.75334185213411</v>
+        <v>-21.43815272832331</v>
       </c>
       <c r="F80">
-        <v>-2.39602386698598</v>
+        <v>-2.714811949911939</v>
       </c>
       <c r="G80">
-        <v>-8.891614642491247</v>
+        <v>-8.295636477976496</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.241431712363405</v>
       </c>
       <c r="E81">
-        <v>-23.20237044772928</v>
+        <v>-21.83173595273201</v>
       </c>
       <c r="F81">
-        <v>-2.347642240458072</v>
+        <v>-2.83418052102275</v>
       </c>
       <c r="G81">
-        <v>-9.55286664327301</v>
+        <v>-8.220606289172492</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.038310407552761</v>
       </c>
       <c r="E82">
-        <v>-24.60750151599057</v>
+        <v>-22.4637010475519</v>
       </c>
       <c r="F82">
-        <v>-2.863857611595445</v>
+        <v>-2.730512825664601</v>
       </c>
       <c r="G82">
-        <v>-9.421460035768504</v>
+        <v>-7.62313347337933</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.8508172479442707</v>
       </c>
       <c r="E83">
-        <v>-25.11754078594746</v>
+        <v>-23.42546850046509</v>
       </c>
       <c r="F83">
-        <v>-1.919097133395984</v>
+        <v>-2.972473145450516</v>
       </c>
       <c r="G83">
-        <v>-8.858949006167236</v>
+        <v>-7.942407956288051</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.6810372739359779</v>
       </c>
       <c r="E84">
-        <v>-24.45208419500416</v>
+        <v>-23.72712869862136</v>
       </c>
       <c r="F84">
-        <v>-2.568007022053005</v>
+        <v>-2.857949695278679</v>
       </c>
       <c r="G84">
-        <v>-8.82804823318682</v>
+        <v>-7.673772780840858</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.5319933120235781</v>
       </c>
       <c r="E85">
-        <v>-26.92275070112949</v>
+        <v>-24.43747735077474</v>
       </c>
       <c r="F85">
-        <v>-2.190042028605855</v>
+        <v>-2.831760859839173</v>
       </c>
       <c r="G85">
-        <v>-9.218323220623162</v>
+        <v>-7.783924011256815</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4050767778580533</v>
       </c>
       <c r="E86">
-        <v>-26.88675066536587</v>
+        <v>-25.65472544512344</v>
       </c>
       <c r="F86">
-        <v>-2.806194128319169</v>
+        <v>-3.015317964258112</v>
       </c>
       <c r="G86">
-        <v>-9.219351853992061</v>
+        <v>-7.445016729022921</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3015675543231707</v>
       </c>
       <c r="E87">
-        <v>-27.92255741656679</v>
+        <v>-26.62193360487215</v>
       </c>
       <c r="F87">
-        <v>-2.529441549248271</v>
+        <v>-3.024158301180789</v>
       </c>
       <c r="G87">
-        <v>-9.323880845931056</v>
+        <v>-7.375440385669752</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2223336795032785</v>
       </c>
       <c r="E88">
-        <v>-29.92514039353864</v>
+        <v>-27.60361985929923</v>
       </c>
       <c r="F88">
-        <v>-2.792373646570862</v>
+        <v>-3.127681032243449</v>
       </c>
       <c r="G88">
-        <v>-8.652871187240004</v>
+        <v>-7.348249480753307</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1686181458814422</v>
       </c>
       <c r="E89">
-        <v>-30.12543108628416</v>
+        <v>-28.76564270266168</v>
       </c>
       <c r="F89">
-        <v>-2.17355917402495</v>
+        <v>-3.198228113735466</v>
       </c>
       <c r="G89">
-        <v>-8.406653170224406</v>
+        <v>-7.510387162839806</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.1421925606210989</v>
       </c>
       <c r="E90">
-        <v>-31.079394655118</v>
+        <v>-30.13212398633412</v>
       </c>
       <c r="F90">
-        <v>-2.771215486368557</v>
+        <v>-3.359024167027683</v>
       </c>
       <c r="G90">
-        <v>-8.169397839390101</v>
+        <v>-7.441714137115163</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1456652168533407</v>
       </c>
       <c r="E91">
-        <v>-32.69941287732592</v>
+        <v>-31.27858059365111</v>
       </c>
       <c r="F91">
-        <v>-2.584931396459601</v>
+        <v>-3.256572515016843</v>
       </c>
       <c r="G91">
-        <v>-8.408863165520783</v>
+        <v>-7.196340695974789</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.1806332845952608</v>
       </c>
       <c r="E92">
-        <v>-33.89496874892504</v>
+        <v>-32.48579660604469</v>
       </c>
       <c r="F92">
-        <v>-2.927239315053247</v>
+        <v>-3.462471516656688</v>
       </c>
       <c r="G92">
-        <v>-9.139823352257569</v>
+        <v>-7.227257133422753</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.2501371817334197</v>
       </c>
       <c r="E93">
-        <v>-35.72165907307907</v>
+        <v>-33.78251847569964</v>
       </c>
       <c r="F93">
-        <v>-2.861910119831464</v>
+        <v>-3.325970650921178</v>
       </c>
       <c r="G93">
-        <v>-8.825571941942149</v>
+        <v>-7.477089726324748</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.3550927311187465</v>
       </c>
       <c r="E94">
-        <v>-37.70015965418391</v>
+        <v>-35.87362299884889</v>
       </c>
       <c r="F94">
-        <v>-2.22380545557656</v>
+        <v>-3.441030054802626</v>
       </c>
       <c r="G94">
-        <v>-9.435293065984519</v>
+        <v>-7.763248219467493</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4967879628420964</v>
       </c>
       <c r="E95">
-        <v>-38.79469489012356</v>
+        <v>-37.57432981067558</v>
       </c>
       <c r="F95">
-        <v>-2.826002878022313</v>
+        <v>-3.553547199124883</v>
       </c>
       <c r="G95">
-        <v>-9.256618927657907</v>
+        <v>-7.772120834960392</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6759259711044183</v>
       </c>
       <c r="E96">
-        <v>-42.08591343430093</v>
+        <v>-38.67713409036296</v>
       </c>
       <c r="F96">
-        <v>-3.124865411441333</v>
+        <v>-3.347629973402176</v>
       </c>
       <c r="G96">
-        <v>-9.734062760874636</v>
+        <v>-8.069837094407994</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8874497631625471</v>
       </c>
       <c r="E97">
-        <v>-42.42150121576972</v>
+        <v>-41.13133934340233</v>
       </c>
       <c r="F97">
-        <v>-3.020420707459357</v>
+        <v>-3.455008754724868</v>
       </c>
       <c r="G97">
-        <v>-9.626316026227096</v>
+        <v>-8.542682101027477</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.131062847474212</v>
       </c>
       <c r="E98">
-        <v>-43.94406433424054</v>
+        <v>-42.56334168893527</v>
       </c>
       <c r="F98">
-        <v>-3.146161080632503</v>
+        <v>-3.615676411069651</v>
       </c>
       <c r="G98">
-        <v>-9.759838642222698</v>
+        <v>-8.689262356095533</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.389567502875112</v>
       </c>
       <c r="E99">
-        <v>-44.67125841152742</v>
+        <v>-44.30655246546025</v>
       </c>
       <c r="F99">
-        <v>-3.606237992882154</v>
+        <v>-3.613911988501688</v>
       </c>
       <c r="G99">
-        <v>-9.797060027858199</v>
+        <v>-8.956613045203898</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.665584286687696</v>
       </c>
       <c r="E100">
-        <v>-48.65102124840281</v>
+        <v>-46.7150588959897</v>
       </c>
       <c r="F100">
-        <v>-3.44298417350583</v>
+        <v>-3.589850400552571</v>
       </c>
       <c r="G100">
-        <v>-9.910560843584555</v>
+        <v>-8.950796306254897</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.92219785051091</v>
       </c>
       <c r="E101">
-        <v>-48.75960799679329</v>
+        <v>-48.7612256726043</v>
       </c>
       <c r="F101">
-        <v>-3.539096329783046</v>
+        <v>-3.855399310500606</v>
       </c>
       <c r="G101">
-        <v>-10.41692911612623</v>
+        <v>-9.520159235035543</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.182410487792147</v>
       </c>
       <c r="E102">
-        <v>-51.64667235543742</v>
+        <v>-50.66289184419981</v>
       </c>
       <c r="F102">
-        <v>-3.519262729057817</v>
+        <v>-3.728947369728456</v>
       </c>
       <c r="G102">
-        <v>-10.14688022248295</v>
+        <v>-9.609408844255046</v>
       </c>
     </row>
   </sheetData>
